--- a/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Exclude #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -140,6 +141,33 @@
   </si>
   <si>
     <t>LP217195-9</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>44851-4</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp # 2 identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>44852-2</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp # 3 identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>44854-8</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp # 4 identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>44855-5</t>
+  </si>
+  <si>
+    <t>Mycobacterium sp # 5 identified in Specimen by Organism specific culture</t>
   </si>
 </sst>
 </file>
@@ -569,4 +597,74 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
+++ b/ValueSet-mii-vs-mikrobio-spezifische-kultur-tests-loinc.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
